--- a/3_Component_Results/PRIVCON/Tables/ifo_tbl/ifo_qoq_forecast_error_table_first_eval.xlsx
+++ b/3_Component_Results/PRIVCON/Tables/ifo_tbl/ifo_qoq_forecast_error_table_first_eval.xlsx
@@ -447,22 +447,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.2225774455180299</v>
+        <v>0.2239730028958191</v>
       </c>
       <c r="C2">
-        <v>0.6025194276978968</v>
+        <v>0.5966084084953039</v>
       </c>
       <c r="D2">
-        <v>0.9375366183193465</v>
+        <v>0.9211822874795074</v>
       </c>
       <c r="E2">
-        <v>0.968264745986007</v>
+        <v>0.9597824167380372</v>
       </c>
       <c r="F2">
-        <v>0.9517120452360237</v>
+        <v>0.9423890774231942</v>
       </c>
       <c r="G2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -470,22 +470,22 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>0.5002927602626792</v>
+        <v>0.49744675377053</v>
       </c>
       <c r="C3">
-        <v>0.8093331159883599</v>
+        <v>0.8004274946780601</v>
       </c>
       <c r="D3">
-        <v>2.512481039783275</v>
+        <v>2.465689823045314</v>
       </c>
       <c r="E3">
-        <v>1.585080767589865</v>
+        <v>1.570251515855124</v>
       </c>
       <c r="F3">
-        <v>1.519327252374612</v>
+        <v>1.504194562286623</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -493,22 +493,22 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>0.7210151913624349</v>
+        <v>0.7162978161184475</v>
       </c>
       <c r="C4">
-        <v>1.262988772388277</v>
+        <v>1.247431925523772</v>
       </c>
       <c r="D4">
-        <v>6.435165304488891</v>
+        <v>6.311169339553707</v>
       </c>
       <c r="E4">
-        <v>2.536762760781719</v>
+        <v>2.512204079997026</v>
       </c>
       <c r="F4">
-        <v>2.457343660326128</v>
+        <v>2.432368203988267</v>
       </c>
       <c r="G4">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -516,22 +516,22 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>0.4586541891000874</v>
+        <v>0.4581744388972914</v>
       </c>
       <c r="C5">
-        <v>1.384892259048143</v>
+        <v>1.365509691091304</v>
       </c>
       <c r="D5">
-        <v>7.994179379982225</v>
+        <v>7.834897197019595</v>
       </c>
       <c r="E5">
-        <v>2.82739798754654</v>
+        <v>2.799088636863719</v>
       </c>
       <c r="F5">
-        <v>2.819473144954236</v>
+        <v>2.78995107352365</v>
       </c>
       <c r="G5">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -539,22 +539,22 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>0.4309535499285895</v>
+        <v>0.4377075682459743</v>
       </c>
       <c r="C6">
-        <v>1.407201242206765</v>
+        <v>1.393616766935021</v>
       </c>
       <c r="D6">
-        <v>8.132525087741485</v>
+        <v>7.974977609444321</v>
       </c>
       <c r="E6">
-        <v>2.85175824496774</v>
+        <v>2.824000284958258</v>
       </c>
       <c r="F6">
-        <v>2.84948429316084</v>
+        <v>2.81939598676563</v>
       </c>
       <c r="G6">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -562,22 +562,22 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>0.436267056338538</v>
+        <v>0.444443450257116</v>
       </c>
       <c r="C7">
-        <v>1.569053982142953</v>
+        <v>1.548184557451162</v>
       </c>
       <c r="D7">
-        <v>9.223627919858613</v>
+        <v>9.001746335102618</v>
       </c>
       <c r="E7">
-        <v>3.037042627270584</v>
+        <v>3.000291041732888</v>
       </c>
       <c r="F7">
-        <v>3.045889392437618</v>
+        <v>3.005978419532529</v>
       </c>
       <c r="G7">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -585,22 +585,22 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>0.4110347441899493</v>
+        <v>0.4148271569523996</v>
       </c>
       <c r="C8">
-        <v>1.588476331609555</v>
+        <v>1.561283439439911</v>
       </c>
       <c r="D8">
-        <v>9.491981118609186</v>
+        <v>9.250302340693484</v>
       </c>
       <c r="E8">
-        <v>3.080905892527259</v>
+        <v>3.041430969246793</v>
       </c>
       <c r="F8">
-        <v>3.095481328727775</v>
+        <v>3.05345346921665</v>
       </c>
       <c r="G8">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -608,22 +608,22 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>0.08076273096934439</v>
+        <v>0.1033524308833308</v>
       </c>
       <c r="C9">
-        <v>2.109961141030493</v>
+        <v>2.035922345227282</v>
       </c>
       <c r="D9">
-        <v>15.00836014869273</v>
+        <v>14.30835193007938</v>
       </c>
       <c r="E9">
-        <v>3.874062486420776</v>
+        <v>3.782638223525927</v>
       </c>
       <c r="F9">
-        <v>3.973840450533185</v>
+        <v>3.874603684941905</v>
       </c>
       <c r="G9">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -631,22 +631,22 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>-0.6203614576892605</v>
+        <v>-0.5435394657712364</v>
       </c>
       <c r="C10">
-        <v>2.00672458876966</v>
+        <v>1.89589757736919</v>
       </c>
       <c r="D10">
-        <v>12.86991326340611</v>
+        <v>11.96543076401852</v>
       </c>
       <c r="E10">
-        <v>3.587466134112782</v>
+        <v>3.459108377027023</v>
       </c>
       <c r="F10">
-        <v>3.677701320433923</v>
+        <v>3.545093451999723</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7">
